--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,52 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Unit Price</t>
+          <t>Price L1</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Price L2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Price L3</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Make</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Specification</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SkillSet</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
         </is>
       </c>
     </row>
@@ -463,14 +498,29 @@
       <c r="D2" t="n">
         <v>150</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>supa</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>9980155233.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -489,14 +539,29 @@
       <c r="D3" t="n">
         <v>45.5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>supa</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>9980155233.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -515,14 +580,29 @@
       <c r="D4" t="n">
         <v>320</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>supb</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -541,14 +621,29 @@
       <c r="D5" t="n">
         <v>85</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>supb</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -567,14 +662,29 @@
       <c r="D6" t="n">
         <v>143</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>supc</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -593,12 +703,31 @@
       <c r="D7" t="n">
         <v>150</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Services" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,24 +430,24 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Make</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Specification</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Price L1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Price L2</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Price L3</t>
-        </is>
-      </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>Supplier</t>
@@ -458,26 +459,6 @@
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Make</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Specification</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>SkillSet</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
@@ -494,6 +475,224 @@
           <t>Hardware</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MakeA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>150</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>supa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9980155233</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Heavy Duty Bracket</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>supa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>9980155233</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Power Supply Unit 500W</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>320</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>supb</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Copper Wiring (100m)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Raw Material</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>85</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>supb</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test item</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>testor</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>143</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>supc</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>SkillSet</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Price L1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Price L2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Price L3</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Service1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>150</v>
@@ -506,224 +705,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>supa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>9980155233.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Heavy Duty Bracket</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>supa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>9980155233.0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Power Supply Unit 500W</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>320</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>supb</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Copper Wiring (100m)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Raw Material</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
-        <v>85</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>supb</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Test item</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>testor</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>143</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>supc</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Service1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
-        <v>150</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,6 +618,51 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Test2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>testor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mtest</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>tmodel</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>nospec</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9980155233</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -499,7 +499,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>01-04-2025</t>
+          <t>07-08-2026</t>
         </is>
       </c>
     </row>
